--- a/docs/all/01_TablasDescriptivas/idx4_Capacidad_summary_labels.xlsx
+++ b/docs/all/01_TablasDescriptivas/idx4_Capacidad_summary_labels.xlsx
@@ -406,10 +406,10 @@
         <v>125</v>
       </c>
       <c r="D2">
-        <v>6.175999999999998</v>
+        <v>6.176</v>
       </c>
       <c r="E2">
-        <v>8.476784235058833</v>
+        <v>8.476784235058831</v>
       </c>
       <c r="F2">
         <v>1</v>
